--- a/dados_site/projetos.xlsx
+++ b/dados_site/projetos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,11 +793,7 @@
           <t>Adequação Climática e Uso Racional de Água em Edificações</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Simulação termo-energética e caracterização dos usos finais de água e energia</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Esta pesquisa avalia o desempenho termo-energético e os usos finais de energia e água em edificações residenciais, comerciais e públicas no Brasil. Por meio de simulações computacionais e medições de materiais, busca estabelecer diretrizes de projeto adequadas às diferentes zonas bioclimáticas brasileiras. Os resultados subsidiam a formulação de normas técnicas de sustentabilidade, eficiência energética e conservação de recursos hídricos.</t>
@@ -813,11 +809,7 @@
           <t>Climate Adaptation and Rational Use of Water in Buildings</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Thermo-energetic simulation and end-use characterization of water and energy</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>This research evaluates thermo-energetic performance and water and energy end-uses in residential, commercial, and public buildings in Brazil. Through computer simulations and material testing, it aims to establish design guidelines tailored to different Brazilian bioclimatic zones. The findings support the development of technical standards for sustainability, energy efficiency, and water conservation.</t>
@@ -833,11 +825,7 @@
           <t>Adecuación Climática y Uso Racional del Agua en Edificaciones</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Simulación termoenergética y caracterización de usos finales de agua y energía</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Esta investigación evalúa el desempeño termoenergético y los usos finales de energía y agua en edificaciones residenciales, comerciales y públicas en Brasil. Mediante simulaciones computacionales y mediciones de materiales, busca establecer directrices de diseño adecuadas a las diferentes zonas bioclimáticas brasileñas. Los resultados subsidian la formulación de normas técnicas de sostenibilidad, eficiencia energética y conservación de recursos hídricos.</t>
@@ -853,11 +841,7 @@
           <t>建筑气候适应与合理用水</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>水与能源末端用能特征分析与热能模拟</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>该研究评估了巴西住宅、商业和公共建筑的热能性能以及水和能源的末端用途。通过计算机模拟和材料性能测量，旨在建立适应巴西不同生物气候区的建筑设计指南。研究结果为制定可持续性、能源效率和水资源保护的技术标准提供了数据支撑。</t>
@@ -1127,6 +1111,124 @@
           <t>2015 - 2018</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rainwater4all</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>em_andamento</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Rainwater4All</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Soluções sustentáveis para melhorar a segurança hídrica em cidades localizadas em Santa Catarina</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>O projeto tem como objetivo identificar soluções sustentáveis para melhorar a segurança hídrica em cidades de Santa Catarina, com foco no uso de telhados verdes e pavimentos permeáveis para o filtrado e aproveitamento de água de chuva em edificações. A pesquisa abrange revisões sobre soluções baseadas na natureza (NbS), simulações computacionais para avaliar os impactos das mudanças climáticas no abastecimento hídrico e ensaios com modelos físicos.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rainwater4All, Segurança Hídrica, Telhado Verde, Pavimento Permeável</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rainwater4All</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sustainable solutions to improve water security in cities located in Santa Catarina</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>The project aims to identify sustainable solutions to improve water security in cities in Santa Catarina, focusing on the use of green roofs and permeable pavements for filtering and harvesting rainwater in buildings. The research covers state-of-the-art reviews on nature-based solutions (NbS), computer simulations to assess climate change impacts on water supply, and tests with physical models of permeable pavements.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Rainwater4All, Water Security, Green Roofs, Permeable Pavements</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Rainwater4All</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Soluciones sostenibles para mejorar la seguridad hídrica en ciudades localizadas en Santa Catarina</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>El proyecto tiene como objetivo identificar soluciones sostenibles para mejorar la seguridad hídrica en ciudades de Santa Catarina, con foco en el uso de techos verdes y pavimentos permeables para el filtrado y aprovechamiento de agua de lluvia en edificaciones. La investigación abarca revisiones sobre soluciones basadas en la naturaleza (NbS), simulaciones computacionales para evaluar los impactos del cambio climático en el suministro hídrico y ensayos con modelos físicos.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Rainwater4All, Seguridad Hídrica, Techo Verde, Pavimento Permeable</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Rainwater4All</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>旨在提高圣卡塔琳娜州城市水安全的可持续解决方案</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>该项目旨在确定提高圣卡塔琳娜州城市水安全的可持续解决方案，重点是利用绿色屋顶和透水铺装对建筑物中的雨水进行过滤和收集。研究包括对基于自然的解决方案（NbS）的最新综述、评估气候变化对供水影响的计算机模拟，以及透水铺装物理模型的实验测试。</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Rainwater4All, 水安全, 绿色屋顶, 透水铺装</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Enedir Ghisi</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Enedir Ghisi - Coordenador / Liseane Padilha Thives - Integrante / Andrea Teston - Integrante</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Graduação: (1) / Mestrado: (2) / Doutorado: (1)</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>FEESC</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2024 - Atual</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
